--- a/results/01_pollution_assessment/HZD_Toxicity/tables/hzd_site_scores.xlsx
+++ b/results/01_pollution_assessment/HZD_Toxicity/tables/hzd_site_scores.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mean_TEC_quotient</t>
+          <t>HZD_Toxicity_Percent</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -452,11 +452,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>546.8862872709975</v>
+        <v>100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -467,11 +467,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>360.6353167654386</v>
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>323.051407701296</v>
+        <v>100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -497,11 +497,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2556.139459613995</v>
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -512,11 +512,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>389.1447595169337</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>323.0207538464629</v>
+        <v>100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -542,11 +542,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>965.0597246895593</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>626.3454772460516</v>
+        <v>100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -572,11 +572,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>555.7541358872287</v>
+        <v>100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.2944182421847</v>
+        <v>100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -602,11 +602,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>455.2901281447499</v>
+        <v>100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>367.9311051558853</v>
+        <v>100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>245.1926159538724</v>
+        <v>100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>856.6217823212094</v>
+        <v>100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -662,11 +662,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3855.607461612087</v>
+        <v>100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -677,11 +677,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1149.724994108823</v>
+        <v>100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>207.0579438659458</v>
+        <v>100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2039.584531727344</v>
+        <v>100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>337.3607090928327</v>
+        <v>100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -737,11 +737,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1280.055962132029</v>
+        <v>100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -752,11 +752,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1336.455020765899</v>
+        <v>100</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1260.930648651318</v>
+        <v>100</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -782,11 +782,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>724.5505919915011</v>
+        <v>100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>498.4759345244664</v>
+        <v>100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>294.0369370837824</v>
+        <v>100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>291.8593637161068</v>
+        <v>100</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>620.0084421057505</v>
+        <v>100</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>370.5239447808135</v>
+        <v>100</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>360.7196949436424</v>
+        <v>100</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1547.418445218523</v>
+        <v>100</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2444.610007996022</v>
+        <v>100</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -917,11 +917,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>406.5795781388446</v>
+        <v>100</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -932,11 +932,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2022.805759516662</v>
+        <v>100</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -947,11 +947,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>631.9144309478047</v>
+        <v>100</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -962,11 +962,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2844.226360015358</v>
+        <v>100</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -977,11 +977,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1032.145332995505</v>
+        <v>100</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -992,11 +992,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>234.7532068771725</v>
+        <v>100</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>328.1116646398809</v>
+        <v>100</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2039.298832631272</v>
+        <v>100</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2936.464886550528</v>
+        <v>100</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1052,11 +1052,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>404.8127038009187</v>
+        <v>100</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1067,11 +1067,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1434.537304015319</v>
+        <v>100</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1082,11 +1082,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>480.5934958009264</v>
+        <v>100</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1097,11 +1097,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1595.603088504419</v>
+        <v>100</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>327.0548948471127</v>
+        <v>100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2567.921701705455</v>
+        <v>100</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2925.875750432383</v>
+        <v>100</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2686.191880139867</v>
+        <v>100</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1172,11 +1172,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2524.560294320388</v>
+        <v>100</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1187,11 +1187,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>683.8857100183628</v>
+        <v>100</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1202,11 +1202,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3220.618650230261</v>
+        <v>100</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2321.289901301369</v>
+        <v>100</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1232,11 +1232,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>396.6112299329343</v>
+        <v>100</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1041.460472141753</v>
+        <v>100</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1262,11 +1262,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>259.7106245630908</v>
+        <v>100</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1277,11 +1277,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3618.987219158857</v>
+        <v>100</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>95.30282091625358</v>
+        <v>100</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1307,11 +1307,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1868.516971161154</v>
+        <v>100</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>360.3018697066473</v>
+        <v>100</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1131.118265712656</v>
+        <v>100</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1352,11 +1352,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>757.2518796502143</v>
+        <v>100</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>396.6243555823813</v>
+        <v>100</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1382,11 +1382,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2427.207442015336</v>
+        <v>100</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1397,11 +1397,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1207.542886770313</v>
+        <v>100</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>474.3285163878188</v>
+        <v>100</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2024.762538137933</v>
+        <v>100</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1442,11 +1442,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>955.5179229718462</v>
+        <v>100</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1457,11 +1457,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>771.5957150011114</v>
+        <v>100</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3219.427834099502</v>
+        <v>100</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2862.402128390998</v>
+        <v>100</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1502,11 +1502,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1334.429688323259</v>
+        <v>100</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2015.888612882292</v>
+        <v>100</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1033.684920906245</v>
+        <v>100</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1256.055857684058</v>
+        <v>100</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>533.1034047186363</v>
+        <v>100</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1577,11 +1577,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>454.5250660126463</v>
+        <v>100</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1592,11 +1592,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2311.968018222636</v>
+        <v>100</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2808.049236778268</v>
+        <v>100</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1622,11 +1622,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1685.684089901667</v>
+        <v>100</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1180.338209126076</v>
+        <v>100</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1122.274824173758</v>
+        <v>100</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1667,11 +1667,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1659.615220500805</v>
+        <v>100</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>496.5426573352681</v>
+        <v>100</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1697,11 +1697,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>515.3802232348582</v>
+        <v>100</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1712,11 +1712,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>535.0407758200341</v>
+        <v>100</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2218.983006704507</v>
+        <v>100</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1413.758615588961</v>
+        <v>100</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1757,11 +1757,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2489.46694485589</v>
+        <v>100</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1772,11 +1772,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3824.762156001866</v>
+        <v>100</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1787,11 +1787,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>363.8787590418078</v>
+        <v>100</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1802,11 +1802,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>891.0246999633022</v>
+        <v>100</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1817,11 +1817,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>370.47640217286</v>
+        <v>100</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1832,11 +1832,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>441.6795858714871</v>
+        <v>100</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>987.6297528963544</v>
+        <v>100</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1862,11 +1862,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>283.2726392272232</v>
+        <v>100</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1877,11 +1877,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>381.4001161546993</v>
+        <v>100</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1892,11 +1892,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>373.1704849866163</v>
+        <v>100</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1907,11 +1907,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>875.5709275513107</v>
+        <v>100</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1922,11 +1922,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1358.858232890638</v>
+        <v>100</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1937,11 +1937,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>181.1997641153565</v>
+        <v>100</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1952,11 +1952,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3179.781182840011</v>
+        <v>100</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3142.640102524054</v>
+        <v>100</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1982,11 +1982,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>441.136470741838</v>
+        <v>100</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1039.188751641183</v>
+        <v>100</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2012,11 +2012,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>963.859908813514</v>
+        <v>100</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2027,11 +2027,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>910.127316173354</v>
+        <v>100</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2042,11 +2042,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>428.0664505928089</v>
+        <v>100</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2694.184434639124</v>
+        <v>100</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2003.593883557836</v>
+        <v>100</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>169.9943731212041</v>
+        <v>100</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2102,11 +2102,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>515.9467661722379</v>
+        <v>100</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>250.7853030719525</v>
+        <v>100</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2132,11 +2132,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>583.505704203978</v>
+        <v>100</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2147,11 +2147,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>311.7563898753855</v>
+        <v>100</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2162,11 +2162,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>198.2376242625456</v>
+        <v>100</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2177,11 +2177,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>513.1136162930709</v>
+        <v>100</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2192,11 +2192,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>336.9837854810057</v>
+        <v>100</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2207,11 +2207,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>496.7402313037054</v>
+        <v>100</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2222,11 +2222,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>336.3256766938426</v>
+        <v>100</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2237,11 +2237,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>793.5918378849225</v>
+        <v>100</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2252,11 +2252,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>255.8564348346725</v>
+        <v>100</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>343.7205495724889</v>
+        <v>100</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2282,11 +2282,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>296.5898617084659</v>
+        <v>100</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2297,11 +2297,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>401.0753779079404</v>
+        <v>100</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2312,11 +2312,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2031.289738977498</v>
+        <v>100</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2327,11 +2327,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>351.1248217609392</v>
+        <v>100</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2342,11 +2342,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1095.356525225187</v>
+        <v>100</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2357,11 +2357,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>394.6835944254109</v>
+        <v>100</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.2391400530769594</v>
+        <v>0</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2387,11 +2387,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4643949513019008</v>
+        <v>8.884823624232311</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2402,11 +2402,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4002670072052598</v>
+        <v>0</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4020971603219171</v>
+        <v>0</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2432,11 +2432,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.7883675856260133</v>
+        <v>39.37860290006312</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2447,11 +2447,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.1712090236995696</v>
+        <v>0</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2462,11 +2462,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4432991395385336</v>
+        <v>9.246115318539733</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2477,11 +2477,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.9124762053984454</v>
+        <v>41.21690915865982</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2492,11 +2492,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4741477832316837</v>
+        <v>5.192854952948649</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2507,11 +2507,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.2096002130555716</v>
+        <v>0</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2522,11 +2522,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1.020408690917624</v>
+        <v>63.07306397379421</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2537,11 +2537,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3924751554334691</v>
+        <v>7.023559361226481</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2552,11 +2552,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.6242582123737723</v>
+        <v>15.54628086949784</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2567,11 +2567,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.9485972043021773</v>
+        <v>59.74430768299121</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.13026320128465</v>
+        <v>0</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2597,11 +2597,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.7343143234177123</v>
+        <v>19.88353183245006</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2612,11 +2612,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.135455148277309</v>
+        <v>0</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2627,11 +2627,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.2318267311054871</v>
+        <v>0</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5205546767190856</v>
+        <v>0</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2657,11 +2657,11 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.2270161697541991</v>
+        <v>0</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2672,11 +2672,11 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.1825130642224894</v>
+        <v>0</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.7299454178590239</v>
+        <v>46.07658715304557</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2702,11 +2702,11 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.6495339628492859</v>
+        <v>34.26612528957411</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2717,11 +2717,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.2610463830819818</v>
+        <v>0</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2732,11 +2732,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.3071558901585077</v>
+        <v>6.266701781214498</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2747,11 +2747,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5029826617408119</v>
+        <v>10.4822261573836</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2762,11 +2762,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.3286767233116691</v>
+        <v>0</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2777,11 +2777,11 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.1965487616287194</v>
+        <v>0</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.1908842765115448</v>
+        <v>0</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2807,11 +2807,11 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.2184919676865521</v>
+        <v>0</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2822,11 +2822,11 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.2144050107363134</v>
+        <v>0</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2837,11 +2837,11 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.2839703713828352</v>
+        <v>7.390458650182329</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2852,11 +2852,11 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.2677732789849023</v>
+        <v>5.684363316358896</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2867,11 +2867,11 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.4739652129196524</v>
+        <v>22.85963389508339</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2882,11 +2882,11 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.29470335827301</v>
+        <v>7.247474382534291</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2897,11 +2897,11 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.2433912197371346</v>
+        <v>0</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2912,11 +2912,11 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.1431208293142813</v>
+        <v>0</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2927,11 +2927,11 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.8275551189581094</v>
+        <v>35.28677842912137</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.7326150197426464</v>
+        <v>13.42728302628974</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2957,11 +2957,11 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.1557762199960696</v>
+        <v>0</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2972,11 +2972,11 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.1564016836450785</v>
+        <v>0</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2987,11 +2987,11 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.266767498974194</v>
+        <v>5.886788765859095</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3002,11 +3002,11 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.1999314835689022</v>
+        <v>0</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3017,11 +3017,11 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.18029803592388</v>
+        <v>0</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.08996246329549092</v>
+        <v>0</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Minimal</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3047,11 +3047,11 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.1514228442250805</v>
+        <v>0</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3062,11 +3062,11 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.9116693361970298</v>
+        <v>70.68192661380374</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -3077,11 +3077,11 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.7401907753963759</v>
+        <v>48.57835309873153</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3092,11 +3092,11 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.2917440089704874</v>
+        <v>5.405775384698827</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.2851270375879725</v>
+        <v>0</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3122,11 +3122,11 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.2885075946852097</v>
+        <v>0</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3137,11 +3137,11 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.3074288730943942</v>
+        <v>0</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3152,11 +3152,11 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.342972469220203</v>
+        <v>0</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3167,11 +3167,11 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.4273167072928416</v>
+        <v>0</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3182,11 +3182,11 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.2792978200801642</v>
+        <v>0</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3197,11 +3197,11 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.3104283510217224</v>
+        <v>0</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3212,11 +3212,11 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.284801915715939</v>
+        <v>0</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3227,11 +3227,11 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1.893167949228662</v>
+        <v>100</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -3242,11 +3242,11 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.199267293047739</v>
+        <v>0</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3257,11 +3257,11 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.1524763969427995</v>
+        <v>0</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3272,11 +3272,11 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.1344810940920871</v>
+        <v>0</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3287,11 +3287,11 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.1244932670632117</v>
+        <v>0</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3302,11 +3302,11 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.1367514538991493</v>
+        <v>0</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3317,11 +3317,11 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2880780030897398</v>
+        <v>5.720346834762566</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3332,11 +3332,11 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.2411346763675841</v>
+        <v>0</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3347,11 +3347,11 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.7320690379521224</v>
+        <v>44.46845182625755</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3362,11 +3362,11 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.2930096236356986</v>
+        <v>6.213844945247019</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3377,11 +3377,11 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.3284992114284019</v>
+        <v>7.727072983155174</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3392,11 +3392,11 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.4208317153582702</v>
+        <v>11.83054525377548</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3407,11 +3407,11 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.571697566891171</v>
+        <v>12.92588204574501</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3422,11 +3422,11 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.425044294328721</v>
+        <v>7.587488221961018</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3437,11 +3437,11 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.2488937133323992</v>
+        <v>0</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3452,11 +3452,11 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2465965279908351</v>
+        <v>0</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3467,11 +3467,11 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.09396394700554918</v>
+        <v>0</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Minimal</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3482,11 +3482,11 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.2329794090698065</v>
+        <v>0</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3497,11 +3497,11 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.2498395019123729</v>
+        <v>0</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3512,11 +3512,11 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.2213218160288667</v>
+        <v>0</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3527,11 +3527,11 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.1849383963339816</v>
+        <v>0</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3542,11 +3542,11 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.1344287893696847</v>
+        <v>0</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3557,11 +3557,11 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.1486526709572346</v>
+        <v>0</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3572,11 +3572,11 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.1769340715928249</v>
+        <v>0</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3587,11 +3587,11 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.3493690179926907</v>
+        <v>0</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3602,11 +3602,11 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.1941764529315793</v>
+        <v>0</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3617,11 +3617,11 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.1573844351980846</v>
+        <v>0</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3632,11 +3632,11 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.3890146368437</v>
+        <v>6.681902749466157</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3647,11 +3647,11 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.1130597803117607</v>
+        <v>0</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3662,11 +3662,11 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.1834459944775769</v>
+        <v>0</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3677,11 +3677,11 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.7470427322152114</v>
+        <v>34.23421327856809</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3692,11 +3692,11 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.7295156377576173</v>
+        <v>24.58928343490263</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3707,11 +3707,11 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>5.384312685924876</v>
+        <v>100</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -3722,11 +3722,11 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.5130559324059444</v>
+        <v>5.327838802008446</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1.084657664641707</v>
+        <v>40.97335249778372</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3752,11 +3752,11 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.2107433821558446</v>
+        <v>0</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3767,11 +3767,11 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>2.427564381354639</v>
+        <v>100</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -3782,11 +3782,11 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.559125160484891</v>
+        <v>20.99222465691347</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3797,11 +3797,11 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.7207287762010216</v>
+        <v>22.25386589281224</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3812,11 +3812,11 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.3900247357395382</v>
+        <v>5.091373116196439</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3827,11 +3827,11 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.1897280823443891</v>
+        <v>0</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3842,11 +3842,11 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.36626348840349</v>
+        <v>0</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3857,11 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1.424195694697974</v>
+        <v>92.98775109907241</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -3872,11 +3872,11 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.3474352783346483</v>
+        <v>5.405775384698827</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3887,11 +3887,11 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.7409686837677236</v>
+        <v>29.60315858123303</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3902,11 +3902,11 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.6462341331066203</v>
+        <v>19.56039334862705</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3917,11 +3917,11 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.4337643353817396</v>
+        <v>6.292300746884432</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -3932,11 +3932,11 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8025652004222816</v>
+        <v>32.10045861871748</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>

--- a/results/01_pollution_assessment/HZD_Toxicity/tables/hzd_site_scores.xlsx
+++ b/results/01_pollution_assessment/HZD_Toxicity/tables/hzd_site_scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C234"/>
+  <dimension ref="A1:C311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>DR-02</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -478,7 +478,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -493,7 +493,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>007ABC</t>
+          <t>DR-06</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -508,7 +508,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>DR-07</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -523,7 +523,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -538,7 +538,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -553,7 +553,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -568,7 +568,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -583,7 +583,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -598,7 +598,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -613,7 +613,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -628,7 +628,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -643,7 +643,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -658,7 +658,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>DR-87</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -673,7 +673,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -688,7 +688,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -703,7 +703,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>DR-120</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -718,7 +718,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -733,7 +733,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -748,7 +748,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -763,7 +763,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -778,7 +778,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>DR-161</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -793,7 +793,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -808,7 +808,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -823,7 +823,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -838,7 +838,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -853,7 +853,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -868,7 +868,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -883,7 +883,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -898,7 +898,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -913,7 +913,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -928,7 +928,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -943,7 +943,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -958,7 +958,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -973,7 +973,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>DR-180</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -988,7 +988,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1003,7 +1003,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1018,7 +1018,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>DR-184</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1033,7 +1033,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1048,7 +1048,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>DR-187</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1063,7 +1063,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1078,7 +1078,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1093,7 +1093,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>DR-190</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1108,7 +1108,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1123,7 +1123,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1138,7 +1138,7 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1153,7 +1153,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1168,7 +1168,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1183,7 +1183,7 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1198,7 +1198,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1213,7 +1213,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1228,7 +1228,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1243,7 +1243,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1258,7 +1258,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1273,7 +1273,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1288,7 +1288,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1303,7 +1303,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1318,7 +1318,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1333,7 +1333,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1348,7 +1348,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1363,7 +1363,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1378,7 +1378,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>DR-210</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1393,7 +1393,7 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>DR-211</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1408,7 +1408,7 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>DR-212</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1423,7 +1423,7 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>DR-213</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1438,7 +1438,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>DR-214</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1453,7 +1453,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>DR-215</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1468,7 +1468,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1483,7 +1483,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>DR-217</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1498,7 +1498,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>DR-218</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1513,7 +1513,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>DR-219</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1528,7 +1528,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>DR-220</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1543,7 +1543,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>DR-221</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1558,7 +1558,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1573,7 +1573,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1588,7 +1588,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>DR-224</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1603,7 +1603,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1618,7 +1618,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1633,7 +1633,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1648,7 +1648,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>DR-228</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1663,7 +1663,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>DR-229</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1678,7 +1678,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1693,7 +1693,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1708,7 +1708,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1723,7 +1723,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1738,7 +1738,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>DR-234</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1753,7 +1753,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1768,7 +1768,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1783,7 +1783,7 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1798,7 +1798,7 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>DR-13</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -1813,7 +1813,7 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1828,7 +1828,7 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1843,7 +1843,7 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1858,7 +1858,7 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1873,7 +1873,7 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1888,7 +1888,7 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1903,7 +1903,7 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1918,7 +1918,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1933,7 +1933,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -1948,7 +1948,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1963,7 +1963,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -1978,7 +1978,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -1993,7 +1993,7 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -2008,7 +2008,7 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -2023,7 +2023,7 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -2038,7 +2038,7 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -2053,7 +2053,7 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -2068,7 +2068,7 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>DR-34</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -2083,7 +2083,7 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -2098,7 +2098,7 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2113,7 +2113,7 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2128,7 +2128,7 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -2143,7 +2143,7 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -2158,7 +2158,7 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -2173,7 +2173,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2188,7 +2188,7 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -2203,7 +2203,7 @@
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2218,7 +2218,7 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -2233,7 +2233,7 @@
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>DR-46</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2248,7 +2248,7 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2263,7 +2263,7 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -2278,7 +2278,7 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -2293,7 +2293,7 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -2308,7 +2308,7 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -2323,7 +2323,7 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -2338,7 +2338,7 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -2353,7 +2353,7 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -2368,161 +2368,161 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>8.884823624232311</v>
+        <v>100</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>DR-58</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>15.52674927170229</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>DR-60</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>39.37860290006312</v>
+        <v>100</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>DR-61</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>21.95292317875094</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>DR-62</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>9.246115318539733</v>
+        <v>100</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>DR-63</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>41.21690915865982</v>
+        <v>0</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>DR-64</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>5.192854952948649</v>
+        <v>100</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>DR-66</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>47.39628575458646</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>DR-67</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>63.07306397379421</v>
+        <v>100</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2533,11 +2533,11 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>DR-68</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>7.023559361226481</v>
+        <v>32.14458081400629</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -2548,11 +2548,11 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>DR-69</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>15.54628086949784</v>
+        <v>46.9709876193439</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -2563,11 +2563,11 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>DR-70</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>59.74430768299121</v>
+        <v>100</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -2593,11 +2593,11 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>DR-72</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>19.88353183245006</v>
+        <v>43.59306165406142</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -2608,22 +2608,22 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-73</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -2638,7 +2638,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>DR-75</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -2653,127 +2653,127 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>DR-77</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>DR-78</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>17.68920605879996</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>DR-79</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>46.07658715304557</v>
+        <v>61.64909335186145</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>DR-80</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>34.26612528957411</v>
+        <v>100</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>DR-81</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>DR-82</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>6.266701781214498</v>
+        <v>100</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>DR-83</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>10.4822261573836</v>
+        <v>0</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>DR-84</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -2788,22 +2788,22 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-86</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>12.16206313713817</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -2818,41 +2818,41 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>DR-89</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>12.79047771445277</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-90</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>7.390458650182329</v>
+        <v>99.80128108701081</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>DR-91</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>5.684363316358896</v>
+        <v>15.10557306698044</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -2863,26 +2863,26 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-92</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>22.85963389508339</v>
+        <v>100</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-93</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>7.247474382534291</v>
+        <v>6.398614500872457</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -2908,7 +2908,7 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -2923,11 +2923,11 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>DR-96</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>35.28677842912137</v>
+        <v>5.399972173447412</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -2938,11 +2938,11 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>DR-97</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>13.42728302628974</v>
+        <v>6.64913987141926</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -2953,41 +2953,41 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-99</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>63.14740806455943</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-100</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>10.36277827356558</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>DR-101</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>5.886788765859095</v>
+        <v>18.14381522949363</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -2998,22 +2998,22 @@
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-102</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>53.80319224655121</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -3028,41 +3028,41 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>DR-104</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0</v>
+        <v>8.162342771205225</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-105</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>17.51686962167916</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>DR-106</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>70.68192661380374</v>
+        <v>100</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -3073,11 +3073,11 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>DR-107</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>48.57835309873153</v>
+        <v>12.97930538050281</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3088,11 +3088,11 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>5.405775384698827</v>
+        <v>6.64913987141926</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -3103,127 +3103,127 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>DR-110</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0</v>
+        <v>21.02092076023298</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>DR-111</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0</v>
+        <v>5.164509848990815</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>DR-113</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>62.62135812429021</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>DR-114</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>DR-115</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>DR-116</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>DR-117</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>67.02108883968515</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>DR-118</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3238,52 +3238,52 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>DR-119</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>DR-122</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -3298,7 +3298,7 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3313,11 +3313,11 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>5.720346834762566</v>
+        <v>8.884823624232311</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -3343,26 +3343,26 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>44.46845182625755</v>
+        <v>0</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>6.213844945247019</v>
+        <v>39.37860290006312</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -3373,26 +3373,26 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>7.727072983155174</v>
+        <v>0</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>11.83054525377548</v>
+        <v>9.246115318539733</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -3403,11 +3403,11 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>12.92588204574501</v>
+        <v>41.21690915865982</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3418,11 +3418,11 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>7.587488221961018</v>
+        <v>5.192854952948649</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -3448,112 +3448,112 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>DR-124</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0</v>
+        <v>15.12441545470555</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>26.42408619186319</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>5.327608797529681</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0</v>
+        <v>63.07306397379421</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0</v>
+        <v>7.023559361226481</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>15.54628086949784</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>LSC-11</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0</v>
+        <v>59.74430768299121</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -3568,22 +3568,22 @@
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>DR-128</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -3598,7 +3598,7 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -3613,7 +3613,7 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -3628,11 +3628,11 @@
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>DR-132</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>6.681902749466157</v>
+        <v>5.675400727884027</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -3658,26 +3658,26 @@
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>DR-134</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>28.64083251829923</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>DR-135</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>34.23421327856809</v>
+        <v>44.15082180919537</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -3688,41 +3688,41 @@
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>24.58928343490263</v>
+        <v>0</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>LSC-13</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>100</v>
+        <v>19.88353183245006</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Above PEC</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>5.327838802008446</v>
+        <v>10.32585695167561</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -3733,97 +3733,97 @@
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>DR-138</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>40.97335249778372</v>
+        <v>100</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>DR-139</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>16.36999343467322</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Above PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>20.99222465691347</v>
+        <v>0</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>22.25386589281224</v>
+        <v>0</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>5.091373116196439</v>
+        <v>0</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -3838,56 +3838,56 @@
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0</v>
+        <v>46.07658715304557</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>92.98775109907241</v>
+        <v>34.26612528957411</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Above PEC</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>5.405775384698827</v>
+        <v>0</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>29.60315858123303</v>
+        <v>6.266701781214498</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -3898,11 +3898,11 @@
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>19.56039334862705</v>
+        <v>10.4822261573836</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -3913,28 +3913,1183 @@
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>6.292300746884432</v>
+        <v>0</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>TEC-PEC</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B234" t="n">
+        <v>0</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>SCR-18</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>SCR-19</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>SCR-20</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>LSC-14</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>7.390458650182329</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>LSC-15</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>5.684363316358896</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>LSC-16</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>22.85963389508339</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>LSC-17</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>7.247474382534291</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>LSC-18</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>LSC-19</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>LSC-20</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>35.28677842912137</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>LSC-21</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>13.42728302628974</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>LSC-22</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>LSC-23</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>SCR-05</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>5.886788765859095</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>LSC-24</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>LSC-25</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>LSC-26</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>LSC-27</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>0</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>SCR-06</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>70.68192661380374</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>LSC-28</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>48.57835309873153</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>LSC-29</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>5.405775384698827</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>LSC-30</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>0</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>LSC-31</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>0</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>LSC-32</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>0</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>LSC-33</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>0</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>LSC-34</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>LSC-35</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>LSC-36</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>LSC-37</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>SCR-07</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>100</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>LSC-38</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>0</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>LSC-39</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>LSC-40</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>LSC-41</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>LSC-42</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>LSC-43</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>5.720346834762566</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>LSC-44</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>44.46845182625755</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>LSC-46</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>6.213844945247019</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>7.727072983155174</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>11.83054525377548</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>LSC-49</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>12.92588204574501</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>LSC-50</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>7.587488221961018</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>LSC-51</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>0</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>LSC-52</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>LSC-54</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>LSC-61</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>LSC-63</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>6.681902749466157</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>DR-146</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>34.23421327856809</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>DR-147</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>24.58928343490263</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>DR-148</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>100</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>DR-149</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>5.327838802008446</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>DR-150</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>40.97335249778372</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>DR-151</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>100</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>DR-152</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>20.99222465691347</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>DR-154</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>22.25386589281224</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>DR-155</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>5.091373116196439</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>0</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>DR-158</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>92.98775109907241</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Above PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>5.405775384698827</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>LSC-64</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>29.60315858123303</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>LSC-65</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>19.56039334862705</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>LSC-66</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>6.292300746884432</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>TEC-PEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>LSC-67</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
         <v>32.10045861871748</v>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C311" t="inlineStr">
         <is>
           <t>TEC-PEC</t>
         </is>
